--- a/__fixtures__/simple-multisheet.xlsx
+++ b/__fixtures__/simple-multisheet.xlsx
@@ -1,7 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kendrick/Documents/git/community-db/__fixtures__/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F9D662-6126-6B4F-B41E-E242B28E7CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="1660" yWindow="600" windowWidth="49540" windowHeight="28200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Community" sheetId="1" r:id="rId1"/>
     <sheet name="Property" sheetId="2" r:id="rId2"/>
@@ -11,37 +21,315 @@
     <sheet name="Event" sheetId="6" r:id="rId6"/>
     <sheet name="Ticket" sheetId="7" r:id="rId7"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="99">
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>defaultSetting</t>
+  </si>
+  <si>
+    <t>eventList</t>
+  </si>
+  <si>
+    <t>ticketList</t>
+  </si>
+  <si>
+    <t>paymentMethodList</t>
+  </si>
+  <si>
+    <t>mailchimpSetting</t>
+  </si>
+  <si>
+    <t>geoapifySetting</t>
+  </si>
+  <si>
+    <t>updatedAt</t>
+  </si>
+  <si>
+    <t>updatedBy</t>
+  </si>
+  <si>
+    <t>{"membershipFee":null,"membershipEmail":null}</t>
+  </si>
+  <si>
+    <t>[{"name":"Membership Carry Forward","hidden":false},{"name":"Summer Festival","hidden":false},{"name":"Corn Roast","hidden":false}]</t>
+  </si>
+  <si>
+    <t>[{"name":"meal","count":null,"unitPrice":"5.00","hidden":false},{"name":"drink","count":null,"unitPrice":"1.00","hidden":false},{"name":"cotton-candy","count":null,"unitPrice":null,"hidden":false}]</t>
+  </si>
+  <si>
+    <t>[{"name":"cash","hidden":false},{"name":"e-Transfer","hidden":false},{"name":"free","hidden":false}]</t>
+  </si>
+  <si>
+    <t>2025-09-29T18:29:07.690Z</t>
+  </si>
+  <si>
+    <t>dev@email.com</t>
+  </si>
+  <si>
+    <t>propertyId</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>streetNo</t>
+  </si>
+  <si>
+    <t>streetName</t>
+  </si>
+  <si>
+    <t>postalCode</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>lat</t>
+  </si>
+  <si>
+    <t>lon</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>123 Adventure Drive</t>
+  </si>
+  <si>
+    <t>Adventure Drive</t>
+  </si>
+  <si>
+    <t>A0A0A0</t>
+  </si>
+  <si>
+    <t>2nd entry</t>
+  </si>
+  <si>
+    <t>2023-02-23T03:19:09.000Z</t>
+  </si>
+  <si>
+    <t>test@email.com</t>
+  </si>
+  <si>
+    <t>99 Fortune Drive</t>
+  </si>
+  <si>
+    <t>Fortune Drive</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>occupantId</t>
+  </si>
+  <si>
+    <t>setIndex</t>
+  </si>
+  <si>
+    <t>firstName</t>
+  </si>
+  <si>
+    <t>lastName</t>
+  </si>
+  <si>
+    <t>optOut</t>
+  </si>
+  <si>
+    <t>startDate</t>
+  </si>
+  <si>
+    <t>endDate</t>
+  </si>
+  <si>
+    <t>Kevin</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>First1</t>
+  </si>
+  <si>
+    <t>Last1</t>
+  </si>
+  <si>
+    <t>First2</t>
+  </si>
+  <si>
+    <t>Last2</t>
+  </si>
+  <si>
+    <t>First3</t>
+  </si>
+  <si>
+    <t>Last3</t>
+  </si>
+  <si>
+    <t>contactId</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>label</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>EMAIL</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>ksmith@email.com</t>
+  </si>
+  <si>
+    <t>Email1</t>
+  </si>
+  <si>
+    <t>PHONE</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>4161234567</t>
+  </si>
+  <si>
+    <t>work</t>
+  </si>
+  <si>
+    <t>4162345678</t>
+  </si>
+  <si>
+    <t>cell</t>
+  </si>
+  <si>
+    <t>4163456789</t>
+  </si>
+  <si>
+    <t>Email2</t>
+  </si>
+  <si>
+    <t>4171234567</t>
+  </si>
+  <si>
+    <t>Email3</t>
+  </si>
+  <si>
+    <t>membershipId</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>isMember</t>
+  </si>
+  <si>
+    <t>paymentMethod</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>paymentDeposited</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>e-Transfer</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>free</t>
+  </si>
+  <si>
+    <t>eventId</t>
+  </si>
+  <si>
+    <t>eventName</t>
+  </si>
+  <si>
+    <t>eventDate</t>
+  </si>
+  <si>
+    <t>Corn Roast</t>
+  </si>
+  <si>
+    <t>2023-08-20T00:00:00.000Z</t>
+  </si>
+  <si>
+    <t>Summer Festival</t>
+  </si>
+  <si>
+    <t>2023-06-11T00:00:00.000Z</t>
+  </si>
+  <si>
+    <t>Membership Carry Forward</t>
+  </si>
+  <si>
+    <t>2022-02-10T00:00:00.000Z</t>
+  </si>
+  <si>
+    <t>2021-01-23T00:00:00.000Z</t>
+  </si>
+  <si>
+    <t>ticketId</t>
+  </si>
+  <si>
+    <t>ticketName</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>meal</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>drink</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>cotton-candy</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Sample Community</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -71,13 +359,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -402,451 +698,493 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>defaultSetting</v>
-      </c>
-      <c r="C1" t="str">
-        <v>eventList</v>
-      </c>
-      <c r="D1" t="str">
-        <v>ticketList</v>
-      </c>
-      <c r="E1" t="str">
-        <v>paymentMethodList</v>
-      </c>
-      <c r="F1" t="str">
-        <v>mailchimpSetting</v>
-      </c>
-      <c r="G1" t="str">
-        <v>geoapifySetting</v>
-      </c>
-      <c r="H1" t="str">
-        <v>updatedAt</v>
-      </c>
-      <c r="I1" t="str">
-        <v>updatedBy</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Sample Community</v>
-      </c>
-      <c r="B2" t="str">
-        <v>{"membershipFee":null,"membershipEmail":null}</v>
-      </c>
-      <c r="C2" t="str">
-        <v>[{"name":"Membership Carry Forward","hidden":false},{"name":"Summer Festival","hidden":false},{"name":"Corn Roast","hidden":false}]</v>
-      </c>
-      <c r="D2" t="str">
-        <v>[{"name":"meal","count":null,"unitPrice":"5.00","hidden":false},{"name":"drink","count":null,"unitPrice":"1.00","hidden":false},{"name":"cotton-candy","count":null,"unitPrice":null,"hidden":false}]</v>
-      </c>
-      <c r="E2" t="str">
-        <v>[{"name":"cash","hidden":false},{"name":"e-Transfer","hidden":false},{"name":"free","hidden":false}]</v>
-      </c>
-      <c r="H2" t="str">
-        <v>2025-09-29T18:29:07.690Z</v>
-      </c>
-      <c r="I2" t="str">
-        <v>dev@email.com</v>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+    <ignoredError sqref="A1:I1 B2:I2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>propertyId</v>
-      </c>
-      <c r="B1" t="str">
-        <v>address</v>
-      </c>
-      <c r="C1" t="str">
-        <v>streetNo</v>
-      </c>
-      <c r="D1" t="str">
-        <v>streetName</v>
-      </c>
-      <c r="E1" t="str">
-        <v>postalCode</v>
-      </c>
-      <c r="F1" t="str">
-        <v>city</v>
-      </c>
-      <c r="G1" t="str">
-        <v>country</v>
-      </c>
-      <c r="H1" t="str">
-        <v>lat</v>
-      </c>
-      <c r="I1" t="str">
-        <v>lon</v>
-      </c>
-      <c r="J1" t="str">
-        <v>notes</v>
-      </c>
-      <c r="K1" t="str">
-        <v>updatedAt</v>
-      </c>
-      <c r="L1" t="str">
-        <v>updatedBy</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>123 Adventure Drive</v>
+      <c r="B2" t="s">
+        <v>25</v>
       </c>
       <c r="C2">
         <v>123</v>
       </c>
-      <c r="D2" t="str">
-        <v>Adventure Drive</v>
-      </c>
-      <c r="E2" t="str">
-        <v>A0A0A0</v>
-      </c>
-      <c r="J2" t="str">
-        <v>2nd entry</v>
-      </c>
-      <c r="K2" t="str">
-        <v>2023-02-23T03:19:09.000Z</v>
-      </c>
-      <c r="L2" t="str">
-        <v>test@email.com</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>99 Fortune Drive</v>
+      <c r="B3" t="s">
+        <v>31</v>
       </c>
       <c r="C3">
         <v>99</v>
       </c>
-      <c r="D3" t="str">
-        <v>Fortune Drive</v>
-      </c>
-      <c r="E3" t="str">
-        <v>A0A0A0</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Notes</v>
-      </c>
-      <c r="K3" t="str">
-        <v>2023-02-23T03:19:09.000Z</v>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError sqref="A1:L3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>occupantId</v>
-      </c>
-      <c r="B1" t="str">
-        <v>propertyId</v>
-      </c>
-      <c r="C1" t="str">
-        <v>firstName</v>
-      </c>
-      <c r="D1" t="str">
-        <v>lastName</v>
-      </c>
-      <c r="E1" t="str">
-        <v>optOut</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="str">
-        <v>Kevin</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Smith</v>
-      </c>
-      <c r="E2">
+      <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3">
+      <c r="G2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="str">
-        <v>First1</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Last1</v>
-      </c>
-      <c r="E3">
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4">
+      <c r="G3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
-      <c r="C4" t="str">
-        <v>First2</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Last2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="D4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" t="str">
-        <v>First3</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Last3</v>
+      <c r="D5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError sqref="A1:H1 A5:B5 A2:B2 D2:H2 A3:B3 D3:H3 A4:B4 D4:H4 D5:H5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>contactId</v>
-      </c>
-      <c r="B1" t="str">
-        <v>occupantId</v>
-      </c>
-      <c r="C1" t="str">
-        <v>type</v>
-      </c>
-      <c r="D1" t="str">
-        <v>label</v>
-      </c>
-      <c r="E1" t="str">
-        <v>value</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="str">
-        <v>EMAIL</v>
-      </c>
-      <c r="D2" t="str">
-        <v>email</v>
-      </c>
-      <c r="E2" t="str">
-        <v>ksmith@email.com</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="str">
-        <v>EMAIL</v>
-      </c>
-      <c r="D3" t="str">
-        <v>email</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Email1</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="C3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
-      <c r="C4" t="str">
-        <v>PHONE</v>
-      </c>
-      <c r="D4" t="str">
-        <v>home</v>
-      </c>
-      <c r="E4" t="str">
-        <v>4161234567</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" t="str">
-        <v>PHONE</v>
-      </c>
-      <c r="D5" t="str">
-        <v>work</v>
-      </c>
-      <c r="E5" t="str">
-        <v>4162345678</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="C5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" t="str">
-        <v>PHONE</v>
-      </c>
-      <c r="D6" t="str">
-        <v>cell</v>
-      </c>
-      <c r="E6" t="str">
-        <v>4163456789</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="C6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7" t="str">
-        <v>EMAIL</v>
-      </c>
-      <c r="D7" t="str">
-        <v>email</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Email2</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="C7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
         <v>3</v>
       </c>
-      <c r="C8" t="str">
-        <v>PHONE</v>
-      </c>
-      <c r="D8" t="str">
-        <v>home</v>
-      </c>
-      <c r="E8" t="str">
-        <v>4171234567</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="C8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
-      <c r="C9" t="str">
-        <v>EMAIL</v>
-      </c>
-      <c r="D9" t="str">
-        <v>email</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Email3</v>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
+    <ignoredError sqref="A1:E9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>membershipId</v>
-      </c>
-      <c r="B1" t="str">
-        <v>propertyId</v>
-      </c>
-      <c r="C1" t="str">
-        <v>year</v>
-      </c>
-      <c r="D1" t="str">
-        <v>isMember</v>
-      </c>
-      <c r="E1" t="str">
-        <v>paymentMethod</v>
-      </c>
-      <c r="F1" t="str">
-        <v>price</v>
-      </c>
-      <c r="G1" t="str">
-        <v>paymentDeposited</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -863,7 +1201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -876,17 +1214,17 @@
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" t="str">
-        <v>cash</v>
-      </c>
-      <c r="F3" t="str">
-        <v>20</v>
+      <c r="E3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" t="s">
+        <v>75</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -900,7 +1238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -917,7 +1255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -934,7 +1272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -947,17 +1285,17 @@
       <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7" t="str">
-        <v>e-Transfer</v>
-      </c>
-      <c r="F7" t="str">
-        <v>10</v>
+      <c r="E7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" t="s">
+        <v>77</v>
       </c>
       <c r="G7">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -970,14 +1308,14 @@
       <c r="D8">
         <v>1</v>
       </c>
-      <c r="E8" t="str">
-        <v>free</v>
+      <c r="E8" t="s">
+        <v>78</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -990,262 +1328,268 @@
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" t="str">
-        <v>free</v>
+      <c r="E9" t="s">
+        <v>78</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G9"/>
+    <ignoredError sqref="A1:G9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>eventId</v>
-      </c>
-      <c r="B1" t="str">
-        <v>membershipId</v>
-      </c>
-      <c r="C1" t="str">
-        <v>eventName</v>
-      </c>
-      <c r="D1" t="str">
-        <v>eventDate</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
-      <c r="C2" t="str">
-        <v>Corn Roast</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2023-08-20T00:00:00.000Z</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="C2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>6</v>
       </c>
-      <c r="C3" t="str">
-        <v>Summer Festival</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2023-06-11T00:00:00.000Z</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
         <v>6</v>
       </c>
-      <c r="C4" t="str">
-        <v>Corn Roast</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2023-08-20T00:00:00.000Z</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="C4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
         <v>7</v>
       </c>
-      <c r="C5" t="str">
-        <v>Membership Carry Forward</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2022-02-10T00:00:00.000Z</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
         <v>8</v>
       </c>
-      <c r="C6" t="str">
-        <v>Membership Carry Forward</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2021-01-23T00:00:00.000Z</v>
+      <c r="C6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError sqref="A1:D6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ticketId</v>
-      </c>
-      <c r="B1" t="str">
-        <v>eventId</v>
-      </c>
-      <c r="C1" t="str">
-        <v>ticketName</v>
-      </c>
-      <c r="D1" t="str">
-        <v>count</v>
-      </c>
-      <c r="E1" t="str">
-        <v>price</v>
-      </c>
-      <c r="F1" t="str">
-        <v>paymentMethod</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="str">
-        <v>meal</v>
+      <c r="C2" t="s">
+        <v>92</v>
       </c>
       <c r="D2">
         <v>20</v>
       </c>
-      <c r="E2" t="str">
-        <v>0</v>
-      </c>
-      <c r="F2" t="str">
-        <v>free</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="E2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" t="str">
-        <v>drink</v>
+      <c r="C3" t="s">
+        <v>94</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" t="str">
-        <v>1</v>
-      </c>
-      <c r="F3" t="str">
-        <v>cash</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="E3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
-      <c r="C4" t="str">
-        <v>meal</v>
+      <c r="C4" t="s">
+        <v>92</v>
       </c>
       <c r="D4">
         <v>20</v>
       </c>
-      <c r="E4" t="str">
-        <v>0</v>
-      </c>
-      <c r="F4" t="str">
-        <v>free</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="E4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" t="str">
-        <v>cotton-candy</v>
+      <c r="C5" t="s">
+        <v>96</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" t="str">
-        <v>1</v>
-      </c>
-      <c r="F5" t="str">
-        <v>cash</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="E5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
-      <c r="C6" t="str">
-        <v>meal</v>
+      <c r="C6" t="s">
+        <v>92</v>
       </c>
       <c r="D6">
         <v>10</v>
       </c>
-      <c r="E6" t="str">
-        <v>5</v>
-      </c>
-      <c r="F6" t="str">
-        <v>cash</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="E6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7" t="str">
-        <v>drink</v>
+      <c r="C7" t="s">
+        <v>94</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7" t="str">
-        <v>1</v>
-      </c>
-      <c r="F7" t="str">
-        <v>e-Transfer</v>
+      <c r="E7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+    <ignoredError sqref="A1:F7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/__fixtures__/simple-multisheet.xlsx
+++ b/__fixtures__/simple-multisheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kendrick/Documents/git/community-db/__fixtures__/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F9D662-6126-6B4F-B41E-E242B28E7CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C2A49E-6EE0-DC47-B36E-AAC76D187E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1660" yWindow="600" windowWidth="49540" windowHeight="28200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1720" yWindow="600" windowWidth="49480" windowHeight="28200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Community" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="103">
   <si>
     <t>name</t>
   </si>
@@ -323,19 +323,36 @@
   </si>
   <si>
     <t>Sample Community</t>
+  </si>
+  <si>
+    <t>Previous</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>2010-01-01T00:00:00.000Z</t>
+  </si>
+  <si>
+    <t>2015-02-01T00:00:00.000Z</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF11181C"/>
+      <name val="Inter"/>
     </font>
   </fonts>
   <fills count="2">
@@ -358,8 +375,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -700,9 +718,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -731,7 +749,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>98</v>
       </c>
@@ -765,9 +783,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -805,7 +823,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12">
       <c r="A2">
         <v>1</v>
       </c>
@@ -831,7 +849,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12">
       <c r="A3">
         <v>2</v>
       </c>
@@ -864,10 +882,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>34</v>
       </c>
@@ -893,7 +911,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
@@ -916,7 +934,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
@@ -939,7 +957,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
@@ -962,7 +980,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
@@ -980,6 +998,29 @@
       </c>
       <c r="H5" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -993,9 +1034,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>50</v>
       </c>
@@ -1012,7 +1053,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1029,7 +1070,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1046,7 +1087,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1063,7 +1104,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1080,7 +1121,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1097,7 +1138,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1114,7 +1155,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1131,7 +1172,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1159,9 +1200,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>68</v>
       </c>
@@ -1184,7 +1225,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1201,7 +1242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1224,7 +1265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1238,7 +1279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1255,7 +1296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1272,7 +1313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1295,7 +1336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1315,7 +1356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1346,9 +1387,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>79</v>
       </c>
@@ -1362,7 +1403,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1376,7 +1417,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1390,7 +1431,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1404,7 +1445,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1418,7 +1459,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1444,9 +1485,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>89</v>
       </c>
@@ -1466,7 +1507,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1486,7 +1527,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1506,7 +1547,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1526,7 +1567,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1546,7 +1587,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1566,7 +1607,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>

--- a/__fixtures__/simple-multisheet.xlsx
+++ b/__fixtures__/simple-multisheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kendrick/Documents/git/community-db/__fixtures__/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C2A49E-6EE0-DC47-B36E-AAC76D187E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20152DC3-3FF2-914B-BDC8-6E5C3B7BB792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1720" yWindow="600" windowWidth="49480" windowHeight="28200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1720" yWindow="600" windowWidth="49480" windowHeight="28200" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Community" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="106">
   <si>
     <t>name</t>
   </si>
@@ -335,6 +335,15 @@
   </si>
   <si>
     <t>2015-02-01T00:00:00.000Z</t>
+  </si>
+  <si>
+    <t>paymentDate</t>
+  </si>
+  <si>
+    <t>2023-08-21T00:00:00.000Z</t>
+  </si>
+  <si>
+    <t>2023-06-12T00:00:00.000Z</t>
   </si>
 </sst>
 </file>
@@ -1484,10 +1493,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>89</v>
       </c>
@@ -1506,8 +1515,11 @@
       <c r="F1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1527,7 +1539,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1546,8 +1558,11 @@
       <c r="F3" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1567,7 +1582,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1586,8 +1601,11 @@
       <c r="F5" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1607,7 +1625,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1629,6 +1647,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <ignoredErrors>
     <ignoredError sqref="A1:F7" numberStoredAsText="1"/>
   </ignoredErrors>

--- a/__fixtures__/simple-multisheet.xlsx
+++ b/__fixtures__/simple-multisheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kendrick/Documents/git/community-db/__fixtures__/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20152DC3-3FF2-914B-BDC8-6E5C3B7BB792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A01BB7-4746-F448-912F-22C0C2E5859F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1720" yWindow="600" windowWidth="49480" windowHeight="28200" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="600" windowWidth="49760" windowHeight="28200" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Community" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="106">
   <si>
     <t>name</t>
   </si>
@@ -55,6 +55,9 @@
     <t>updatedBy</t>
   </si>
   <si>
+    <t>Sample Community</t>
+  </si>
+  <si>
     <t>{"membershipFee":null,"membershipEmail":null}</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t>[{"name":"cash","hidden":false},{"name":"e-Transfer","hidden":false},{"name":"free","hidden":false}]</t>
   </si>
   <si>
+    <t>{"apiKey":"7RBvsiJ5YFMdzt6N5zQgaA=="}</t>
+  </si>
+  <si>
     <t>2025-09-29T18:29:07.690Z</t>
   </si>
   <si>
@@ -145,10 +151,10 @@
     <t>optOut</t>
   </si>
   <si>
-    <t>startDate</t>
-  </si>
-  <si>
-    <t>endDate</t>
+    <t>moveInDate</t>
+  </si>
+  <si>
+    <t>moveOutDate</t>
   </si>
   <si>
     <t>Kevin</t>
@@ -178,6 +184,12 @@
     <t>Last3</t>
   </si>
   <si>
+    <t>Previous</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
     <t>contactId</t>
   </si>
   <si>
@@ -241,30 +253,57 @@
     <t>isMember</t>
   </si>
   <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>paymentEventName</t>
+  </si>
+  <si>
+    <t>paymentDate</t>
+  </si>
+  <si>
     <t>paymentMethod</t>
   </si>
   <si>
-    <t>price</t>
-  </si>
-  <si>
     <t>paymentDeposited</t>
   </si>
   <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Corn Roast</t>
+  </si>
+  <si>
+    <t>2023-08-20T00:00:00.000Z</t>
+  </si>
+  <si>
     <t>cash</t>
   </si>
   <si>
-    <t>20</t>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Summer Festival</t>
+  </si>
+  <si>
+    <t>2023-06-11T00:00:00.000Z</t>
   </si>
   <si>
     <t>e-Transfer</t>
   </si>
   <si>
-    <t>10</t>
+    <t>Membership Carry Forward</t>
+  </si>
+  <si>
+    <t>2022-02-10T00:00:00.000Z</t>
   </si>
   <si>
     <t>free</t>
   </si>
   <si>
+    <t>2021-01-23T00:00:00.000Z</t>
+  </si>
+  <si>
     <t>eventId</t>
   </si>
   <si>
@@ -274,27 +313,6 @@
     <t>eventDate</t>
   </si>
   <si>
-    <t>Corn Roast</t>
-  </si>
-  <si>
-    <t>2023-08-20T00:00:00.000Z</t>
-  </si>
-  <si>
-    <t>Summer Festival</t>
-  </si>
-  <si>
-    <t>2023-06-11T00:00:00.000Z</t>
-  </si>
-  <si>
-    <t>Membership Carry Forward</t>
-  </si>
-  <si>
-    <t>2022-02-10T00:00:00.000Z</t>
-  </si>
-  <si>
-    <t>2021-01-23T00:00:00.000Z</t>
-  </si>
-  <si>
     <t>ticketId</t>
   </si>
   <si>
@@ -316,52 +334,29 @@
     <t>1</t>
   </si>
   <si>
+    <t>2023-08-21T00:00:00.000Z</t>
+  </si>
+  <si>
     <t>cotton-candy</t>
   </si>
   <si>
+    <t>2023-06-12T00:00:00.000Z</t>
+  </si>
+  <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>Sample Community</t>
-  </si>
-  <si>
-    <t>Previous</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>2010-01-01T00:00:00.000Z</t>
-  </si>
-  <si>
-    <t>2015-02-01T00:00:00.000Z</t>
-  </si>
-  <si>
-    <t>paymentDate</t>
-  </si>
-  <si>
-    <t>2023-08-21T00:00:00.000Z</t>
-  </si>
-  <si>
-    <t>2023-06-12T00:00:00.000Z</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF11181C"/>
-      <name val="Inter"/>
     </font>
   </fonts>
   <fills count="2">
@@ -384,9 +379,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -727,9 +721,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -758,33 +752,36 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I1 B2:I2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -792,38 +789,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K1" t="s">
         <v>7</v>
@@ -832,53 +829,53 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2">
         <v>123</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C3">
         <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -892,124 +889,136 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="18">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1020,22 +1029,22 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>102</v>
+        <v>53</v>
+      </c>
+      <c r="G6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H1 A5:B5 A2:B2 D2:H2 A3:B3 D3:H3 A4:B4 D4:H4 D5:H5" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1043,26 +1052,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1070,16 +1079,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1087,16 +1096,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1104,16 +1113,16 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1121,16 +1130,16 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1138,16 +1147,16 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1155,16 +1164,16 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1172,16 +1181,16 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1189,13 +1198,13 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1208,33 +1217,39 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>77</v>
+      </c>
+      <c r="H1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1247,11 +1262,8 @@
       <c r="D2">
         <v>0</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1265,16 +1277,22 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="G3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1288,7 +1306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1301,11 +1319,8 @@
       <c r="D5">
         <v>0</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1318,11 +1333,8 @@
       <c r="D6">
         <v>0</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1336,16 +1348,22 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>85</v>
+      </c>
+      <c r="G7" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1358,14 +1376,23 @@
       <c r="D8">
         <v>1</v>
       </c>
-      <c r="E8" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8">
+      <c r="E8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="F8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8" t="s">
+        <v>90</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1378,17 +1405,26 @@
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" t="s">
-        <v>78</v>
-      </c>
-      <c r="G9">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G9" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I7 A9:D9 A8:D8 F8:I8 F9:I9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1396,37 +1432,37 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="B1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>82</v>
       </c>
-      <c r="D2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1434,13 +1470,13 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1448,13 +1484,13 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" t="s">
         <v>82</v>
       </c>
-      <c r="D4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1462,13 +1498,13 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1476,15 +1512,14 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <ignoredErrors>
     <ignoredError sqref="A1:D6" numberStoredAsText="1"/>
   </ignoredErrors>
@@ -1494,32 +1529,32 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F1" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1527,19 +1562,22 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D2">
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>90</v>
+      </c>
+      <c r="G2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1547,22 +1585,22 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F3" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1570,19 +1608,22 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D4">
         <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>90</v>
+      </c>
+      <c r="G4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1590,22 +1631,22 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F5" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1613,19 +1654,22 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D6">
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>83</v>
+      </c>
+      <c r="G6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1633,23 +1677,25 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s">
-        <v>76</v>
+        <v>87</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F7" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>